--- a/artfynd/A 36730-2025 artfynd.xlsx
+++ b/artfynd/A 36730-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129930249</v>
       </c>
       <c r="B2" t="n">
-        <v>92873</v>
+        <v>92876</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36730-2025 artfynd.xlsx
+++ b/artfynd/A 36730-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129930249</v>
       </c>
       <c r="B2" t="n">
-        <v>92876</v>
+        <v>92879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36730-2025 artfynd.xlsx
+++ b/artfynd/A 36730-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129930249</v>
       </c>
       <c r="B2" t="n">
-        <v>92879</v>
+        <v>92880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36730-2025 artfynd.xlsx
+++ b/artfynd/A 36730-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129930249</v>
       </c>
       <c r="B2" t="n">
-        <v>92880</v>
+        <v>92897</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36730-2025 artfynd.xlsx
+++ b/artfynd/A 36730-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129930249</v>
       </c>
       <c r="B2" t="n">
-        <v>92913</v>
+        <v>92915</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36730-2025 artfynd.xlsx
+++ b/artfynd/A 36730-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129930249</v>
       </c>
       <c r="B2" t="n">
-        <v>92915</v>
+        <v>93002</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
